--- a/outputs/per-fund/vc-investments-robot-ventures.xlsx
+++ b/outputs/per-fund/vc-investments-robot-ventures.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Robot Ventures. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Robot Ventures. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -21696,11 +21696,11 @@
         <v>2</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, robot-ventures</t>
+          <t>arrington-capital, lemniscap, robot-ventures</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -21948,11 +21948,11 @@
         <v>1</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, framework-ventures, robot-ventures</t>
+          <t>coinbase-ventures, digital-currency-group, electric-capital, framework-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -22011,11 +22011,11 @@
         <v>2</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>mechanism-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -22070,11 +22070,11 @@
         <v>0</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>cms-holdings, mechanism-capital, robot-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -22131,11 +22131,11 @@
         <v>0</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>huobi-ventures, parafi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -22377,11 +22377,11 @@
         <v>1</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, electric-capital, robot-ventures</t>
+          <t>alliance-dao, coinfund, delphi-ventures, electric-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -22434,11 +22434,11 @@
         <v>0</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>alameda-research, cms-holdings, iosg-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -22560,11 +22560,11 @@
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>polychain, robot-ventures</t>
+          <t>blockchain-capital, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -22619,11 +22619,11 @@
         <v>1</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, dragonfly, paradigm, robot-ventures</t>
+          <t>alameda-research, coinbase-ventures, delphi-ventures, digital-currency-group, dragonfly, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -22678,11 +22678,11 @@
         <v>2</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital, robot-ventures</t>
+          <t>alameda-research, alliance-dao, delphi-ventures, fenbushi-capital, iosg-ventures, multicoin-capital, okx-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -22798,11 +22798,11 @@
         <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>alameda-research, cms-holdings, parafi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -22861,11 +22861,11 @@
         <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>blockchain-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -22924,11 +22924,11 @@
         <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, lemniscap, polychain, robot-ventures</t>
+          <t>dragonfly, galaxy-digital, lemniscap, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -22983,11 +22983,11 @@
         <v>1</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, polychain, robot-ventures</t>
+          <t>alliance-dao, electric-capital, iosg-ventures, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -23046,11 +23046,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, robot-ventures</t>
+          <t>alliance-dao, framework-ventures, parafi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -23109,11 +23109,11 @@
         <v>2</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, robot-ventures</t>
+          <t>alliance-dao, framework-ventures, parafi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -23231,11 +23231,11 @@
         <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, paradigm, robot-ventures</t>
+          <t>delphi-ventures, mechanism-capital, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -23294,11 +23294,11 @@
         <v>2</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital, robot-ventures</t>
+          <t>delphi-ventures, hypersphere, multicoin-capital, robot-ventures, spartan-group, yzi-labs</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -23536,11 +23536,11 @@
         <v>1</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures, robot-ventures</t>
+          <t>amber-group, coinbase-ventures, framework-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -23599,11 +23599,11 @@
         <v>0</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>1kx, robot-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -23910,11 +23910,11 @@
         <v>0</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>paradigm, robot-ventures</t>
+          <t>alameda-research, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -23971,11 +23971,11 @@
         <v>0</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, robot-ventures</t>
+          <t>1kx, blockchain-capital, delphi-ventures, hack-vc, longhash-ventures, robot-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -24034,11 +24034,11 @@
         <v>1</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, gnosis-vc, polychain, robot-ventures</t>
+          <t>1kx, amber-group, circle-ventures, figment-capital, gnosis-vc, hack-vc, hypersphere, polychain, polygon-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -24156,11 +24156,11 @@
         <v>1</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, robot-ventures</t>
+          <t>alliance-dao, dragonfly, robot-ventures</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -24408,11 +24408,11 @@
         <v>0</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, robot-ventures</t>
+          <t>arrington-capital, lemniscap, parafi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -24471,11 +24471,11 @@
         <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures, multicoin-capital, robot-ventures</t>
+          <t>alameda-research, delphi-ventures, framework-ventures, multicoin-capital, robot-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -24597,11 +24597,11 @@
         <v>0</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>galaxy-digital, jump-crypto, robot-ventures</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -24660,11 +24660,11 @@
         <v>1</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>haun-ventures, paradigm, robot-ventures</t>
+          <t>circle-ventures, haun-ventures, paradigm, polygon-ventures, robot-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -24723,11 +24723,11 @@
         <v>0</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, robot-ventures</t>
+          <t>coinbase-ventures, polygon-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -24849,11 +24849,11 @@
         <v>1</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>blockchain-capital, fenbushi-capital, hack-vc, iosg-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr">
@@ -24912,11 +24912,11 @@
         <v>0</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>polygon-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -24975,11 +24975,11 @@
         <v>2</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, paradigm, robot-ventures</t>
+          <t>bain-capital-crypto, jump-crypto, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
@@ -25038,11 +25038,11 @@
         <v>1</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>haun-ventures, maven11, robot-ventures</t>
+          <t>1kx, haun-ventures, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -25227,11 +25227,11 @@
         <v>2</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>circle-ventures, parafi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -25290,11 +25290,11 @@
         <v>1</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, robot-ventures</t>
+          <t>circle-ventures, coinbase-ventures, electric-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -25353,11 +25353,11 @@
         <v>2</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>maven11, robot-ventures</t>
+          <t>galaxy-digital, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -25481,11 +25481,11 @@
         <v>1</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>polychain, robot-ventures</t>
+          <t>hack-vc, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -25544,11 +25544,11 @@
         <v>1</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital, lemniscap, maven11, robot-ventures</t>
+          <t>1kx, delphi-ventures, figment-capital, lemniscap, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -25607,11 +25607,11 @@
         <v>1</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>maven11, robot-ventures</t>
+          <t>circle-ventures, foresight-ventures, hashkey-capital, maven11, robot-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
@@ -25733,11 +25733,11 @@
         <v>2</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, robot-ventures</t>
+          <t>fenbushi-capital, figment-capital, iosg-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -25918,11 +25918,11 @@
         <v>1</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, robot-ventures</t>
+          <t>1kx, framework-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
@@ -26233,11 +26233,11 @@
         <v>2</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, robot-ventures</t>
+          <t>hack-vc, multicoin-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
@@ -26359,11 +26359,11 @@
         <v>1</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, robot-ventures</t>
+          <t>gsr, lemniscap, robot-ventures</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
@@ -26422,11 +26422,11 @@
         <v>1</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>cmt-digital, galaxy-digital, robot-ventures</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
@@ -26485,11 +26485,11 @@
         <v>2</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, polychain, robot-ventures</t>
+          <t>bain-capital-crypto, hack-vc, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
@@ -26548,11 +26548,11 @@
         <v>1</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, robot-ventures</t>
+          <t>cmt-digital, coinbase-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M80" s="7" t="inlineStr">
@@ -26611,11 +26611,11 @@
         <v>1</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>hack-vc, hypersphere, robot-ventures</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
@@ -26670,11 +26670,11 @@
         <v>3</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>parafi-capital, robot-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr">
@@ -26731,11 +26731,11 @@
         <v>3</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, polychain, robot-ventures</t>
+          <t>blockchain-capital, coinbase-ventures, fenbushi-capital, hack-vc, hashkey-capital, mirana-ventures, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
@@ -26794,11 +26794,11 @@
         <v>1</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>big-brain-holdings, borderless-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
@@ -26983,11 +26983,11 @@
         <v>0</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, robot-ventures</t>
+          <t>electric-capital, mirana-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
@@ -27046,11 +27046,11 @@
         <v>1</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>1kx, alliance-dao, big-brain-holdings, circle-ventures, fenbushi-capital, gsr, polygon-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M88" s="7" t="inlineStr">
@@ -27111,11 +27111,11 @@
         <v>1</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>amber-group, hashed, robot-ventures</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
@@ -27174,11 +27174,11 @@
         <v>1</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>fenbushi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M90" s="7" t="inlineStr">
@@ -27296,11 +27296,11 @@
         <v>0</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures, robot-ventures</t>
+          <t>amber-group, coinbase-ventures, framework-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
@@ -27548,11 +27548,11 @@
         <v>2</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, robot-ventures</t>
+          <t>coinbase-ventures, hashkey-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M96" s="7" t="inlineStr">
@@ -27611,11 +27611,11 @@
         <v>1</v>
       </c>
       <c r="K97" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, maven11, polychain, robot-ventures</t>
+          <t>figment-capital, hack-vc, maven11, mh-ventures, okx-ventures, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
@@ -27859,11 +27859,11 @@
         <v>1</v>
       </c>
       <c r="K101" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, figment-capital, robot-ventures</t>
+          <t>big-brain-holdings, dragonfly, figment-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
@@ -27922,11 +27922,11 @@
         <v>1</v>
       </c>
       <c r="K102" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>polychain, robot-ventures</t>
+          <t>foresight-ventures, mirana-ventures, okx-ventures, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M102" s="7" t="inlineStr">
@@ -28048,11 +28048,11 @@
         <v>3</v>
       </c>
       <c r="K104" s="6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, founders-fund, framework-ventures, pantera, robot-ventures</t>
+          <t>arrington-capital, delphi-ventures, foresight-ventures, founders-fund, framework-ventures, hack-vc, hashkey-capital, hypersphere, mh-ventures, mirana-ventures, pantera, robot-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M104" s="7" t="inlineStr">
@@ -28166,11 +28166,11 @@
         <v>1</v>
       </c>
       <c r="K106" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>hack-vc, hashkey-capital, mh-ventures, polygon-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M106" s="7" t="inlineStr">
@@ -28223,11 +28223,11 @@
         <v>0</v>
       </c>
       <c r="K107" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>amber-group, borderless-capital, mirana-ventures, robot-ventures, yzi-labs</t>
         </is>
       </c>
       <c r="M107" s="7" t="inlineStr">
@@ -28286,11 +28286,11 @@
         <v>1</v>
       </c>
       <c r="K108" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, pantera, robot-ventures, semantic-ventures</t>
+          <t>a16z-crypto, coinbase-ventures, fenbushi-capital, hack-vc, iosg-ventures, mirana-ventures, pantera, robot-ventures, semantic-ventures</t>
         </is>
       </c>
       <c r="M108" s="7" t="inlineStr">
@@ -28349,11 +28349,11 @@
         <v>1</v>
       </c>
       <c r="K109" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, robot-ventures</t>
+          <t>cmt-digital, dragonfly, parafi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M109" s="7" t="inlineStr">
@@ -28408,11 +28408,11 @@
         <v>1</v>
       </c>
       <c r="K110" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>robot-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M110" s="7" t="inlineStr">
@@ -28471,11 +28471,11 @@
         <v>1</v>
       </c>
       <c r="K111" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, robot-ventures</t>
+          <t>cms-holdings, coinbase-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M111" s="7" t="inlineStr">
@@ -28593,11 +28593,11 @@
         <v>1</v>
       </c>
       <c r="K113" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>multicoin-capital, robot-ventures</t>
+          <t>multicoin-capital, okx-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M113" s="7" t="inlineStr">
@@ -28843,11 +28843,11 @@
         <v>1</v>
       </c>
       <c r="K117" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital, robot-ventures, semantic-ventures</t>
+          <t>delphi-ventures, figment-capital, robot-ventures, semantic-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M117" s="7" t="inlineStr">
@@ -28965,11 +28965,11 @@
         <v>3</v>
       </c>
       <c r="K119" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, robot-ventures</t>
+          <t>electric-capital, hashed, mirana-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M119" s="7" t="inlineStr">
@@ -29085,11 +29085,11 @@
         <v>1</v>
       </c>
       <c r="K121" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, robot-ventures</t>
+          <t>1kx, bain-capital-crypto, robot-ventures</t>
         </is>
       </c>
       <c r="M121" s="7" t="inlineStr">
@@ -29211,11 +29211,11 @@
         <v>1</v>
       </c>
       <c r="K123" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, robot-ventures</t>
+          <t>fenbushi-capital, figment-capital, hack-vc, robot-ventures</t>
         </is>
       </c>
       <c r="M123" s="7" t="inlineStr">
@@ -29274,11 +29274,11 @@
         <v>0</v>
       </c>
       <c r="K124" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>maven11, robot-ventures</t>
+          <t>big-brain-holdings, gsr, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M124" s="7" t="inlineStr">
@@ -29461,11 +29461,11 @@
         <v>1</v>
       </c>
       <c r="K127" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>maven11, robot-ventures</t>
+          <t>alliance-dao, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M127" s="7" t="inlineStr">
@@ -29583,11 +29583,11 @@
         <v>1</v>
       </c>
       <c r="K129" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>mechanism-capital, robot-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M129" s="7" t="inlineStr">
@@ -29646,11 +29646,11 @@
         <v>1</v>
       </c>
       <c r="K130" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>maven11, robot-ventures</t>
+          <t>alliance-dao, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M130" s="7" t="inlineStr">
@@ -29705,11 +29705,11 @@
         <v>1</v>
       </c>
       <c r="K131" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital, robot-ventures</t>
+          <t>alliance-dao, big-brain-holdings, delphi-ventures, figment-capital, mechanism-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M131" s="7" t="inlineStr">
@@ -29768,11 +29768,11 @@
         <v>1</v>
       </c>
       <c r="K132" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>big-brain-holdings, gsr, robot-ventures</t>
         </is>
       </c>
       <c r="M132" s="7" t="inlineStr">
@@ -29831,11 +29831,11 @@
         <v>2</v>
       </c>
       <c r="K133" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, paradigm, robot-ventures</t>
+          <t>bain-capital-crypto, fenbushi-capital, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M133" s="7" t="inlineStr">
@@ -29896,11 +29896,11 @@
         <v>2</v>
       </c>
       <c r="K134" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>1kx, digital-currency-group, galaxy-digital, robot-ventures</t>
         </is>
       </c>
       <c r="M134" s="7" t="inlineStr">
@@ -30018,11 +30018,11 @@
         <v>2</v>
       </c>
       <c r="K136" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, figment-capital, robot-ventures</t>
+          <t>coinbase-ventures, figment-capital, hashkey-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M136" s="7" t="inlineStr">
@@ -30081,11 +30081,11 @@
         <v>1</v>
       </c>
       <c r="K137" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>amber-group, hypersphere, robot-ventures</t>
         </is>
       </c>
       <c r="M137" s="7" t="inlineStr">
@@ -30396,11 +30396,11 @@
         <v>1</v>
       </c>
       <c r="K142" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>1kx, animoca-brands, big-brain-holdings, cms-holdings, cmt-digital, gsr, longhash-ventures, mh-ventures, robot-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M142" s="7" t="inlineStr">
@@ -30459,11 +30459,11 @@
         <v>2</v>
       </c>
       <c r="K143" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, cyber-fund, maven11, robot-ventures</t>
+          <t>arrington-capital, coinbase-ventures, cyber-fund, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M143" s="7" t="inlineStr">
@@ -30522,11 +30522,11 @@
         <v>1</v>
       </c>
       <c r="K144" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, maven11, robot-ventures</t>
+          <t>delphi-ventures, maven11, mechanism-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M144" s="7" t="inlineStr">
@@ -30707,11 +30707,11 @@
         <v>0</v>
       </c>
       <c r="K147" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>pantera, robot-ventures</t>
+          <t>cmt-digital, pantera, robot-ventures</t>
         </is>
       </c>
       <c r="M147" s="7" t="inlineStr">
@@ -30833,11 +30833,11 @@
         <v>1</v>
       </c>
       <c r="K149" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>robot-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M149" s="7" t="inlineStr">
@@ -30959,11 +30959,11 @@
         <v>2</v>
       </c>
       <c r="K151" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>big-brain-holdings, mirana-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M151" s="7" t="inlineStr">
@@ -31138,11 +31138,11 @@
         <v>1</v>
       </c>
       <c r="K154" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>robot-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M154" s="7" t="inlineStr">
@@ -31260,11 +31260,11 @@
         <v>1</v>
       </c>
       <c r="K156" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>robot-ventures</t>
+          <t>blockchain-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M156" s="7" t="inlineStr">
@@ -31323,11 +31323,11 @@
         <v>2</v>
       </c>
       <c r="K157" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, robot-ventures</t>
+          <t>bain-capital-crypto, parafi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M157" s="7" t="inlineStr">
@@ -39500,7 +39500,7 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n">
@@ -39508,13 +39508,13 @@
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Unieke uitgaande domeinen als benadering van portefeuillenamen.</t>
+          <t>Unique outbound domains as an approximation of portfolio names.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -39522,7 +39522,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
